--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1730-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1730-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2239AD1-6A14-4327-97D5-78BC1BE9B193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29603312-70E2-4C59-83FE-5CC0A7E4644C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{CDC4C43D-61FF-4882-B943-BD86FAC43D0B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{DDF4F01E-0D42-414D-933B-654749DDD703}"/>
   </bookViews>
   <sheets>
     <sheet name="1730-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,24 +1484,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB49D9B-CC11-4E09-9502-ADC3E4CE48E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9E027F-222E-4973-A0F9-2AF48EC1E590}">
   <dimension ref="A1:R52"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1655,7 +1655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2024</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2022</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>25</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2021</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2020</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2019</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2018</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2017</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2016</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2015</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2014</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2013</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2012</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2011</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2010</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2009</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2008</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2007</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2006</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2005</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2004</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2003</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2002</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2001</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2000</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1999</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1998</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
         <v>47</v>
       </c>
